--- a/QUOTATION_EXCEL_TEMPLATES/vn_la_land/VN_LA_LAND_2026_QUOTATION.xlsx
+++ b/QUOTATION_EXCEL_TEMPLATES/vn_la_land/VN_LA_LAND_2026_QUOTATION.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\다른 컴퓨터\내 컴퓨터\LK Group 관련\12. 라오-주변국 (베트남, 캄보디아 등등) 운송 관련\고객 견적 확인 요청건\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssapd\StudioProjects\lkgroup_app\QUOTATION_EXCEL_TEMPLATES\vn_la_land\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B712E7-0B27-47BF-B9EB-4722368635F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE88BCA9-FF6C-4FF9-BB9F-A74C82A385B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="120" windowWidth="17808" windowHeight="12192" tabRatio="908" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="375" yWindow="1005" windowWidth="17775" windowHeight="13770" tabRatio="908" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Row data" sheetId="3" r:id="rId1"/>
@@ -1346,7 +1346,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Vietnam-Lao Trucking 가견적</t>
+    <t>Vietnam-Lao Trucking 가견적서</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2316,43 +2316,76 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="6" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="13" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="11" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="14" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="30" fillId="9" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2385,98 +2418,65 @@
     <xf numFmtId="0" fontId="31" fillId="9" borderId="12" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="6" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="13" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="11" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="14" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -2918,8 +2918,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="50800" y="12369800"/>
-          <a:ext cx="8229600" cy="3733800"/>
+          <a:off x="50800" y="12465050"/>
+          <a:ext cx="8280400" cy="3727450"/>
           <a:chOff x="50800" y="15240000"/>
           <a:chExt cx="7899400" cy="3733800"/>
         </a:xfrm>
@@ -3050,8 +3050,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10261600" y="12344400"/>
-          <a:ext cx="7975600" cy="3759200"/>
+          <a:off x="10312400" y="12439650"/>
+          <a:ext cx="8020050" cy="3752850"/>
           <a:chOff x="9118600" y="15214600"/>
           <a:chExt cx="7975600" cy="3719369"/>
         </a:xfrm>
@@ -3188,8 +3188,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="20193000" y="12344399"/>
-          <a:ext cx="8026400" cy="3759201"/>
+          <a:off x="20294600" y="12439649"/>
+          <a:ext cx="8039100" cy="3752851"/>
           <a:chOff x="19761200" y="15214599"/>
           <a:chExt cx="8026400" cy="3747978"/>
         </a:xfrm>
@@ -3328,7 +3328,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$A$1:$N$28" spid="_x0000_s1129"/>
+                  <a14:cameraTool cellRange="$A$1:$N$28" spid="_x0000_s1130"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -3398,7 +3398,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$A$1:$B$9" spid="_x0000_s2074"/>
+                  <a14:cameraTool cellRange="$A$1:$B$9" spid="_x0000_s2075"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -3737,47 +3737,47 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AE61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="15.69921875" style="35" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.59765625" style="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.3984375" style="35" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.75" style="35" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.625" style="35" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.375" style="35" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="4" style="35" customWidth="1"/>
-    <col min="14" max="14" width="15.19921875" style="35" customWidth="1"/>
-    <col min="15" max="15" width="9.69921875" style="35" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.69921875" style="35" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.69921875" style="35" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.59765625" style="35" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="2.59765625" style="49" customWidth="1"/>
-    <col min="20" max="20" width="15.19921875" style="49" customWidth="1"/>
-    <col min="21" max="21" width="9.8984375" style="49" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="26.09765625" style="49" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.69921875" style="49" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.69921875" style="49" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.19921875" style="49" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.25" style="35" customWidth="1"/>
+    <col min="15" max="15" width="9.75" style="35" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.75" style="35" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.75" style="35" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.625" style="35" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="2.625" style="49" customWidth="1"/>
+    <col min="20" max="20" width="15.25" style="49" customWidth="1"/>
+    <col min="21" max="21" width="9.875" style="49" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="26.125" style="49" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.75" style="49" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.75" style="49" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.25" style="49" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="2.5" style="49" customWidth="1"/>
-    <col min="27" max="27" width="27.69921875" style="49" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="27.75" style="49" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="22.5" style="49" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.69921875" style="49" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="9.69921875" style="49" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="37.19921875" style="49" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.75" style="49" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.75" style="49" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="37.25" style="49" bestFit="1" customWidth="1"/>
     <col min="32" max="16384" width="9" style="35"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="173" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="174"/>
-      <c r="C1" s="174"/>
-      <c r="D1" s="174"/>
-      <c r="N1" s="175" t="s">
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="N1" s="174" t="s">
         <v>62</v>
       </c>
-      <c r="O1" s="175"/>
-      <c r="P1" s="175"/>
-      <c r="Q1" s="175"/>
-      <c r="R1" s="175"/>
+      <c r="O1" s="174"/>
+      <c r="P1" s="174"/>
+      <c r="Q1" s="174"/>
+      <c r="R1" s="174"/>
     </row>
     <row r="2" spans="1:31">
       <c r="A2" s="36" t="s">
@@ -3812,24 +3812,24 @@
         <f>B3+C3</f>
         <v>24000</v>
       </c>
-      <c r="N3" s="170" t="s">
+      <c r="N3" s="175" t="s">
         <v>217</v>
       </c>
-      <c r="O3" s="170"/>
-      <c r="P3" s="170"/>
-      <c r="Q3" s="170"/>
-      <c r="T3" s="170" t="s">
+      <c r="O3" s="175"/>
+      <c r="P3" s="175"/>
+      <c r="Q3" s="175"/>
+      <c r="T3" s="175" t="s">
         <v>186</v>
       </c>
-      <c r="U3" s="170"/>
-      <c r="V3" s="170"/>
-      <c r="W3" s="170"/>
-      <c r="AA3" s="170" t="s">
+      <c r="U3" s="175"/>
+      <c r="V3" s="175"/>
+      <c r="W3" s="175"/>
+      <c r="AA3" s="175" t="s">
         <v>187</v>
       </c>
-      <c r="AB3" s="170"/>
-      <c r="AC3" s="170"/>
-      <c r="AD3" s="170"/>
+      <c r="AB3" s="175"/>
+      <c r="AC3" s="175"/>
+      <c r="AD3" s="175"/>
     </row>
     <row r="4" spans="1:31">
       <c r="A4" s="40" t="s">
@@ -3845,31 +3845,31 @@
         <f>B4+C4</f>
         <v>34</v>
       </c>
-      <c r="N4" s="171" t="s">
+      <c r="N4" s="176" t="s">
         <v>63</v>
       </c>
-      <c r="O4" s="172"/>
-      <c r="P4" s="171" t="s">
+      <c r="O4" s="177"/>
+      <c r="P4" s="176" t="s">
         <v>64</v>
       </c>
-      <c r="Q4" s="172"/>
+      <c r="Q4" s="177"/>
       <c r="R4" s="49"/>
-      <c r="T4" s="171" t="s">
+      <c r="T4" s="176" t="s">
         <v>63</v>
       </c>
-      <c r="U4" s="172"/>
-      <c r="V4" s="171" t="s">
+      <c r="U4" s="177"/>
+      <c r="V4" s="176" t="s">
         <v>64</v>
       </c>
-      <c r="W4" s="172"/>
-      <c r="AA4" s="171" t="s">
+      <c r="W4" s="177"/>
+      <c r="AA4" s="176" t="s">
         <v>63</v>
       </c>
-      <c r="AB4" s="172"/>
-      <c r="AC4" s="171" t="s">
+      <c r="AB4" s="177"/>
+      <c r="AC4" s="176" t="s">
         <v>64</v>
       </c>
-      <c r="AD4" s="172"/>
+      <c r="AD4" s="177"/>
     </row>
     <row r="5" spans="1:31">
       <c r="A5" s="42" t="s">
@@ -4556,12 +4556,12 @@
       <c r="AE18" s="61"/>
     </row>
     <row r="19" spans="1:31">
-      <c r="A19" s="173" t="s">
+      <c r="A19" s="171" t="s">
         <v>209</v>
       </c>
-      <c r="B19" s="173"/>
-      <c r="C19" s="173"/>
-      <c r="D19" s="173"/>
+      <c r="B19" s="171"/>
+      <c r="C19" s="171"/>
+      <c r="D19" s="171"/>
       <c r="N19" s="36" t="s">
         <v>101</v>
       </c>
@@ -4651,11 +4651,11 @@
       </c>
       <c r="X21" s="61"/>
       <c r="Y21" s="61"/>
-      <c r="AA21" s="169" t="s">
+      <c r="AA21" s="172" t="s">
         <v>138</v>
       </c>
-      <c r="AB21" s="169"/>
-      <c r="AC21" s="169"/>
+      <c r="AB21" s="172"/>
+      <c r="AC21" s="172"/>
       <c r="AD21" s="61">
         <f>SUM(AD9:AD20)</f>
         <v>0</v>
@@ -4748,12 +4748,12 @@
       </c>
       <c r="X24" s="61"/>
       <c r="Y24" s="61"/>
-      <c r="AA24" s="170" t="s">
+      <c r="AA24" s="175" t="s">
         <v>188</v>
       </c>
-      <c r="AB24" s="170"/>
-      <c r="AC24" s="170"/>
-      <c r="AD24" s="170"/>
+      <c r="AB24" s="175"/>
+      <c r="AC24" s="175"/>
+      <c r="AD24" s="175"/>
       <c r="AE24" s="35"/>
     </row>
     <row r="25" spans="1:31">
@@ -4922,7 +4922,7 @@
       <c r="AD28" s="61"/>
       <c r="AE28" s="47"/>
     </row>
-    <row r="29" spans="1:31" ht="38.4">
+    <row r="29" spans="1:31" ht="34.5">
       <c r="B29" s="45"/>
       <c r="D29" s="45"/>
       <c r="N29" s="36" t="s">
@@ -5062,11 +5062,11 @@
       </c>
       <c r="X32" s="61"/>
       <c r="Y32" s="61"/>
-      <c r="AA32" s="169" t="s">
+      <c r="AA32" s="172" t="s">
         <v>138</v>
       </c>
-      <c r="AB32" s="169"/>
-      <c r="AC32" s="169"/>
+      <c r="AB32" s="172"/>
+      <c r="AC32" s="172"/>
       <c r="AD32" s="61">
         <f>SUM(AD26:AD31)</f>
         <v>0</v>
@@ -5439,12 +5439,12 @@
       </c>
       <c r="Q46" s="51"/>
       <c r="R46" s="51"/>
-      <c r="T46" s="169" t="s">
+      <c r="T46" s="172" t="s">
         <v>302</v>
       </c>
-      <c r="U46" s="169"/>
-      <c r="V46" s="169"/>
-      <c r="W46" s="169"/>
+      <c r="U46" s="172"/>
+      <c r="V46" s="172"/>
+      <c r="W46" s="172"/>
       <c r="X46" s="51">
         <f>SUM(X9:X45)</f>
         <v>0</v>
@@ -5584,11 +5584,11 @@
       <c r="R58" s="51"/>
     </row>
     <row r="59" spans="14:18">
-      <c r="N59" s="169" t="s">
+      <c r="N59" s="172" t="s">
         <v>138</v>
       </c>
-      <c r="O59" s="169"/>
-      <c r="P59" s="169"/>
+      <c r="O59" s="172"/>
+      <c r="P59" s="172"/>
       <c r="Q59" s="54">
         <f>SUM(Q9:Q58)</f>
         <v>0</v>
@@ -5616,11 +5616,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="17">
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="T46:W46"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="N1:R1"/>
-    <mergeCell ref="AA21:AC21"/>
     <mergeCell ref="N59:P59"/>
     <mergeCell ref="N3:Q3"/>
     <mergeCell ref="T3:W3"/>
@@ -5633,6 +5628,11 @@
     <mergeCell ref="AC4:AD4"/>
     <mergeCell ref="AA24:AD24"/>
     <mergeCell ref="AA32:AC32"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="T46:W46"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="N1:R1"/>
+    <mergeCell ref="AA21:AC21"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5647,10 +5647,10 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.59765625" style="55" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="95.09765625" style="55" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.625" style="55" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="95.125" style="55" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="68" style="55" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="55"/>
   </cols>
@@ -5823,7 +5823,7 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="77" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="76" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5834,48 +5834,48 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:W62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="28.19921875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="42.3984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="16.8984375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="39.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="49.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="39.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="41.19921875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="42.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="16.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="39.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="49.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="39.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="41.25" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.5" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" style="1"/>
-    <col min="18" max="18" width="30.8984375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="30.875" style="1" customWidth="1"/>
     <col min="19" max="19" width="9" style="1"/>
-    <col min="20" max="23" width="36.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="36.375" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="162" customHeight="1">
-      <c r="C1" s="141" t="s">
+      <c r="C1" s="152" t="s">
         <v>325</v>
       </c>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="152"/>
+      <c r="I1" s="152"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
       <c r="L1" s="85" t="s">
         <v>258</v>
       </c>
-      <c r="M1" s="137" t="s">
+      <c r="M1" s="148" t="s">
         <v>322</v>
       </c>
-      <c r="N1" s="138"/>
+      <c r="N1" s="149"/>
       <c r="R1" s="23">
         <f>D11</f>
         <v>1</v>
@@ -5893,7 +5893,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="2" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A2" s="22" t="s">
         <v>3</v>
       </c>
@@ -5904,22 +5904,22 @@
       <c r="D2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="139" t="s">
+      <c r="E2" s="150" t="s">
         <v>316</v>
       </c>
-      <c r="F2" s="139"/>
-      <c r="G2" s="140"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="124" t="s">
+      <c r="F2" s="150"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="158" t="s">
         <v>185</v>
       </c>
-      <c r="J2" s="125"/>
-      <c r="K2" s="126"/>
-      <c r="L2" s="133" t="s">
+      <c r="J2" s="159"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="167" t="s">
         <v>243</v>
       </c>
-      <c r="M2" s="134"/>
-      <c r="N2" s="145"/>
+      <c r="M2" s="168"/>
+      <c r="N2" s="156"/>
       <c r="R2" s="24">
         <f>N16</f>
         <v>0</v>
@@ -5939,7 +5939,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="3" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="22" t="s">
         <v>6</v>
       </c>
@@ -5952,12 +5952,12 @@
       <c r="F3" s="123"/>
       <c r="G3" s="123"/>
       <c r="H3" s="123"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="128"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="135"/>
-      <c r="M3" s="136"/>
-      <c r="N3" s="146"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="162"/>
+      <c r="K3" s="163"/>
+      <c r="L3" s="169"/>
+      <c r="M3" s="170"/>
+      <c r="N3" s="157"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
@@ -5976,7 +5976,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="4" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A4" s="22" t="s">
         <v>7</v>
       </c>
@@ -5989,16 +5989,16 @@
       <c r="F4" s="123"/>
       <c r="G4" s="123"/>
       <c r="H4" s="123"/>
-      <c r="I4" s="130" t="s">
+      <c r="I4" s="164" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="131"/>
-      <c r="K4" s="132"/>
-      <c r="L4" s="142" t="s">
+      <c r="J4" s="165"/>
+      <c r="K4" s="166"/>
+      <c r="L4" s="153" t="s">
         <v>244</v>
       </c>
-      <c r="M4" s="143"/>
-      <c r="N4" s="144"/>
+      <c r="M4" s="154"/>
+      <c r="N4" s="155"/>
       <c r="T4" s="33" t="s">
         <v>1</v>
       </c>
@@ -6014,7 +6014,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="5" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A5" s="22" t="s">
         <v>10</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="6" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="6" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A6" s="22">
         <v>1</v>
       </c>
@@ -6097,7 +6097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="7" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A7" s="22">
         <v>2</v>
       </c>
@@ -6119,7 +6119,7 @@
         <v>1800000</v>
       </c>
     </row>
-    <row r="8" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="8" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A8" s="22">
         <v>3</v>
       </c>
@@ -6141,7 +6141,7 @@
         <v>69.230769230769226</v>
       </c>
     </row>
-    <row r="9" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="9" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A9" s="22">
         <v>4</v>
       </c>
@@ -6159,7 +6159,7 @@
       <c r="M9" s="21"/>
       <c r="N9" s="8"/>
     </row>
-    <row r="10" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="10" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A10" s="22">
         <v>5</v>
       </c>
@@ -6177,7 +6177,7 @@
       <c r="M10" s="21"/>
       <c r="N10" s="8"/>
     </row>
-    <row r="11" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="11" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A11" s="123" t="s">
         <v>14</v>
       </c>
@@ -6205,21 +6205,21 @@
       <c r="N11" s="13"/>
     </row>
     <row r="12" spans="1:23" s="2" customFormat="1" ht="54" customHeight="1">
-      <c r="A12" s="165" t="s">
+      <c r="A12" s="124" t="s">
         <v>220</v>
       </c>
-      <c r="B12" s="165"/>
-      <c r="C12" s="165"/>
-      <c r="D12" s="165"/>
-      <c r="E12" s="165"/>
-      <c r="F12" s="165" t="s">
+      <c r="B12" s="124"/>
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="124"/>
+      <c r="F12" s="124" t="s">
         <v>221</v>
       </c>
-      <c r="G12" s="165"/>
-      <c r="H12" s="165"/>
-      <c r="I12" s="165"/>
-      <c r="J12" s="165"/>
-      <c r="K12" s="165"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="124"/>
+      <c r="I12" s="124"/>
+      <c r="J12" s="124"/>
+      <c r="K12" s="124"/>
       <c r="L12" s="123" t="s">
         <v>15</v>
       </c>
@@ -6230,20 +6230,20 @@
       </c>
       <c r="P12" s="23"/>
     </row>
-    <row r="13" spans="1:23" s="2" customFormat="1" ht="52.95" customHeight="1">
-      <c r="A13" s="176" t="s">
+    <row r="13" spans="1:23" s="2" customFormat="1" ht="52.9" customHeight="1">
+      <c r="A13" s="125" t="s">
         <v>324</v>
       </c>
-      <c r="B13" s="177"/>
-      <c r="C13" s="177"/>
-      <c r="D13" s="177"/>
-      <c r="E13" s="177"/>
-      <c r="F13" s="166"/>
-      <c r="G13" s="166"/>
-      <c r="H13" s="166"/>
-      <c r="I13" s="166"/>
-      <c r="J13" s="166"/>
-      <c r="K13" s="166"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="127"/>
+      <c r="G13" s="127"/>
+      <c r="H13" s="127"/>
+      <c r="I13" s="127"/>
+      <c r="J13" s="127"/>
+      <c r="K13" s="127"/>
       <c r="L13" s="89" t="s">
         <v>16</v>
       </c>
@@ -6256,18 +6256,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="2" customFormat="1" ht="52.95" customHeight="1">
-      <c r="A14" s="177"/>
-      <c r="B14" s="177"/>
-      <c r="C14" s="177"/>
-      <c r="D14" s="177"/>
-      <c r="E14" s="177"/>
-      <c r="F14" s="166"/>
-      <c r="G14" s="166"/>
-      <c r="H14" s="166"/>
-      <c r="I14" s="166"/>
-      <c r="J14" s="166"/>
-      <c r="K14" s="166"/>
+    <row r="14" spans="1:23" s="2" customFormat="1" ht="52.9" customHeight="1">
+      <c r="A14" s="126"/>
+      <c r="B14" s="126"/>
+      <c r="C14" s="126"/>
+      <c r="D14" s="126"/>
+      <c r="E14" s="126"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="127"/>
       <c r="L14" s="89" t="s">
         <v>259</v>
       </c>
@@ -6280,18 +6280,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" s="2" customFormat="1" ht="52.95" customHeight="1">
-      <c r="A15" s="177"/>
-      <c r="B15" s="177"/>
-      <c r="C15" s="177"/>
-      <c r="D15" s="177"/>
-      <c r="E15" s="177"/>
-      <c r="F15" s="166"/>
-      <c r="G15" s="166"/>
-      <c r="H15" s="166"/>
-      <c r="I15" s="166"/>
-      <c r="J15" s="166"/>
-      <c r="K15" s="166"/>
+    <row r="15" spans="1:23" s="2" customFormat="1" ht="52.9" customHeight="1">
+      <c r="A15" s="126"/>
+      <c r="B15" s="126"/>
+      <c r="C15" s="126"/>
+      <c r="D15" s="126"/>
+      <c r="E15" s="126"/>
+      <c r="F15" s="127"/>
+      <c r="G15" s="127"/>
+      <c r="H15" s="127"/>
+      <c r="I15" s="127"/>
+      <c r="J15" s="127"/>
+      <c r="K15" s="127"/>
       <c r="L15" s="89" t="s">
         <v>260</v>
       </c>
@@ -6305,18 +6305,18 @@
       </c>
     </row>
     <row r="16" spans="1:23" s="2" customFormat="1" ht="54" customHeight="1">
-      <c r="A16" s="177"/>
-      <c r="B16" s="177"/>
-      <c r="C16" s="177"/>
-      <c r="D16" s="177"/>
-      <c r="E16" s="177"/>
-      <c r="F16" s="166"/>
-      <c r="G16" s="166"/>
-      <c r="H16" s="166"/>
-      <c r="I16" s="166"/>
-      <c r="J16" s="166"/>
-      <c r="K16" s="166"/>
-      <c r="L16" s="167" t="s">
+      <c r="A16" s="126"/>
+      <c r="B16" s="126"/>
+      <c r="C16" s="126"/>
+      <c r="D16" s="126"/>
+      <c r="E16" s="126"/>
+      <c r="F16" s="127"/>
+      <c r="G16" s="127"/>
+      <c r="H16" s="127"/>
+      <c r="I16" s="127"/>
+      <c r="J16" s="127"/>
+      <c r="K16" s="127"/>
+      <c r="L16" s="128" t="s">
         <v>222</v>
       </c>
       <c r="M16" s="86" t="s">
@@ -6328,18 +6328,18 @@
       </c>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="A17" s="177"/>
-      <c r="B17" s="177"/>
-      <c r="C17" s="177"/>
-      <c r="D17" s="177"/>
-      <c r="E17" s="177"/>
-      <c r="F17" s="166"/>
-      <c r="G17" s="166"/>
-      <c r="H17" s="166"/>
-      <c r="I17" s="166"/>
-      <c r="J17" s="166"/>
-      <c r="K17" s="166"/>
-      <c r="L17" s="168"/>
+      <c r="A17" s="126"/>
+      <c r="B17" s="126"/>
+      <c r="C17" s="126"/>
+      <c r="D17" s="126"/>
+      <c r="E17" s="126"/>
+      <c r="F17" s="127"/>
+      <c r="G17" s="127"/>
+      <c r="H17" s="127"/>
+      <c r="I17" s="127"/>
+      <c r="J17" s="127"/>
+      <c r="K17" s="127"/>
+      <c r="L17" s="129"/>
       <c r="M17" s="87" t="s">
         <v>18</v>
       </c>
@@ -6349,18 +6349,18 @@
       </c>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="A18" s="177"/>
-      <c r="B18" s="177"/>
-      <c r="C18" s="177"/>
-      <c r="D18" s="177"/>
-      <c r="E18" s="177"/>
-      <c r="F18" s="166"/>
-      <c r="G18" s="166"/>
-      <c r="H18" s="166"/>
-      <c r="I18" s="166"/>
-      <c r="J18" s="166"/>
-      <c r="K18" s="166"/>
-      <c r="L18" s="168"/>
+      <c r="A18" s="126"/>
+      <c r="B18" s="126"/>
+      <c r="C18" s="126"/>
+      <c r="D18" s="126"/>
+      <c r="E18" s="126"/>
+      <c r="F18" s="127"/>
+      <c r="G18" s="127"/>
+      <c r="H18" s="127"/>
+      <c r="I18" s="127"/>
+      <c r="J18" s="127"/>
+      <c r="K18" s="127"/>
+      <c r="L18" s="129"/>
       <c r="M18" s="88" t="s">
         <v>19</v>
       </c>
@@ -6369,19 +6369,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" s="2" customFormat="1" ht="52.95" customHeight="1">
-      <c r="A19" s="177"/>
-      <c r="B19" s="177"/>
-      <c r="C19" s="177"/>
-      <c r="D19" s="177"/>
-      <c r="E19" s="177"/>
-      <c r="F19" s="166"/>
-      <c r="G19" s="166"/>
-      <c r="H19" s="166"/>
-      <c r="I19" s="166"/>
-      <c r="J19" s="166"/>
-      <c r="K19" s="166"/>
-      <c r="L19" s="168"/>
+    <row r="19" spans="1:14" s="2" customFormat="1" ht="52.9" customHeight="1">
+      <c r="A19" s="126"/>
+      <c r="B19" s="126"/>
+      <c r="C19" s="126"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="126"/>
+      <c r="F19" s="127"/>
+      <c r="G19" s="127"/>
+      <c r="H19" s="127"/>
+      <c r="I19" s="127"/>
+      <c r="J19" s="127"/>
+      <c r="K19" s="127"/>
+      <c r="L19" s="129"/>
       <c r="M19" s="14" t="s">
         <v>20</v>
       </c>
@@ -6406,66 +6406,66 @@
       <c r="M20" s="91"/>
       <c r="N20" s="91"/>
     </row>
-    <row r="21" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A21" s="148" t="s">
+    <row r="21" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A21" s="131" t="s">
         <v>321</v>
       </c>
-      <c r="B21" s="148"/>
-      <c r="C21" s="148"/>
-      <c r="D21" s="148"/>
-      <c r="E21" s="148"/>
-      <c r="F21" s="148"/>
-      <c r="G21" s="148"/>
-      <c r="H21" s="148"/>
-      <c r="I21" s="148"/>
-      <c r="J21" s="148"/>
-      <c r="K21" s="148"/>
-      <c r="L21" s="148"/>
-      <c r="M21" s="148"/>
-      <c r="N21" s="148"/>
-    </row>
-    <row r="22" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A22" s="149" t="s">
+      <c r="B21" s="131"/>
+      <c r="C21" s="131"/>
+      <c r="D21" s="131"/>
+      <c r="E21" s="131"/>
+      <c r="F21" s="131"/>
+      <c r="G21" s="131"/>
+      <c r="H21" s="131"/>
+      <c r="I21" s="131"/>
+      <c r="J21" s="131"/>
+      <c r="K21" s="131"/>
+      <c r="L21" s="131"/>
+      <c r="M21" s="131"/>
+      <c r="N21" s="131"/>
+    </row>
+    <row r="22" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A22" s="132" t="s">
         <v>224</v>
       </c>
-      <c r="B22" s="149"/>
-      <c r="C22" s="149"/>
-      <c r="D22" s="149"/>
-      <c r="E22" s="149"/>
-      <c r="F22" s="149"/>
-      <c r="G22" s="149"/>
-      <c r="H22" s="149"/>
-      <c r="I22" s="149"/>
-      <c r="J22" s="149"/>
-      <c r="K22" s="149"/>
-      <c r="L22" s="149"/>
-      <c r="M22" s="149"/>
-      <c r="N22" s="149"/>
-    </row>
-    <row r="23" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A23" s="149"/>
-      <c r="B23" s="149"/>
-      <c r="C23" s="149"/>
-      <c r="D23" s="149"/>
-      <c r="E23" s="149"/>
-      <c r="F23" s="149"/>
-      <c r="G23" s="149"/>
-      <c r="H23" s="149"/>
-      <c r="I23" s="149"/>
-      <c r="J23" s="149"/>
-      <c r="K23" s="149"/>
-      <c r="L23" s="149"/>
-      <c r="M23" s="149"/>
-      <c r="N23" s="149"/>
-    </row>
-    <row r="24" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A24" s="150" t="s">
+      <c r="B22" s="132"/>
+      <c r="C22" s="132"/>
+      <c r="D22" s="132"/>
+      <c r="E22" s="132"/>
+      <c r="F22" s="132"/>
+      <c r="G22" s="132"/>
+      <c r="H22" s="132"/>
+      <c r="I22" s="132"/>
+      <c r="J22" s="132"/>
+      <c r="K22" s="132"/>
+      <c r="L22" s="132"/>
+      <c r="M22" s="132"/>
+      <c r="N22" s="132"/>
+    </row>
+    <row r="23" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A23" s="132"/>
+      <c r="B23" s="132"/>
+      <c r="C23" s="132"/>
+      <c r="D23" s="132"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="132"/>
+      <c r="H23" s="132"/>
+      <c r="I23" s="132"/>
+      <c r="J23" s="132"/>
+      <c r="K23" s="132"/>
+      <c r="L23" s="132"/>
+      <c r="M23" s="132"/>
+      <c r="N23" s="132"/>
+    </row>
+    <row r="24" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A24" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="151"/>
-      <c r="C24" s="156"/>
-      <c r="D24" s="157"/>
-      <c r="E24" s="158"/>
+      <c r="B24" s="134"/>
+      <c r="C24" s="139"/>
+      <c r="D24" s="140"/>
+      <c r="E24" s="141"/>
       <c r="F24" s="26"/>
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
@@ -6474,75 +6474,75 @@
       <c r="K24" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="L24" s="147"/>
-      <c r="M24" s="147"/>
-      <c r="N24" s="147"/>
-    </row>
-    <row r="25" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A25" s="152"/>
-      <c r="B25" s="153"/>
-      <c r="C25" s="159"/>
-      <c r="D25" s="160"/>
-      <c r="E25" s="161"/>
+      <c r="L24" s="130"/>
+      <c r="M24" s="130"/>
+      <c r="N24" s="130"/>
+    </row>
+    <row r="25" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A25" s="135"/>
+      <c r="B25" s="136"/>
+      <c r="C25" s="142"/>
+      <c r="D25" s="143"/>
+      <c r="E25" s="144"/>
       <c r="F25" s="26"/>
       <c r="G25" s="26"/>
       <c r="H25" s="26"/>
       <c r="I25" s="15"/>
       <c r="J25" s="15"/>
       <c r="K25" s="123"/>
-      <c r="L25" s="147"/>
-      <c r="M25" s="147"/>
-      <c r="N25" s="147"/>
-    </row>
-    <row r="26" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A26" s="152"/>
-      <c r="B26" s="153"/>
-      <c r="C26" s="159"/>
-      <c r="D26" s="160"/>
-      <c r="E26" s="161"/>
+      <c r="L25" s="130"/>
+      <c r="M25" s="130"/>
+      <c r="N25" s="130"/>
+    </row>
+    <row r="26" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A26" s="135"/>
+      <c r="B26" s="136"/>
+      <c r="C26" s="142"/>
+      <c r="D26" s="143"/>
+      <c r="E26" s="144"/>
       <c r="F26" s="26"/>
       <c r="G26" s="26"/>
       <c r="H26" s="26"/>
       <c r="I26" s="15"/>
       <c r="J26" s="15"/>
       <c r="K26" s="123"/>
-      <c r="L26" s="147"/>
-      <c r="M26" s="147"/>
-      <c r="N26" s="147"/>
-    </row>
-    <row r="27" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A27" s="152"/>
-      <c r="B27" s="153"/>
-      <c r="C27" s="159"/>
-      <c r="D27" s="160"/>
-      <c r="E27" s="161"/>
+      <c r="L26" s="130"/>
+      <c r="M26" s="130"/>
+      <c r="N26" s="130"/>
+    </row>
+    <row r="27" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A27" s="135"/>
+      <c r="B27" s="136"/>
+      <c r="C27" s="142"/>
+      <c r="D27" s="143"/>
+      <c r="E27" s="144"/>
       <c r="F27" s="26"/>
       <c r="G27" s="26"/>
       <c r="H27" s="26"/>
       <c r="I27" s="15"/>
       <c r="J27" s="15"/>
       <c r="K27" s="123"/>
-      <c r="L27" s="147"/>
-      <c r="M27" s="147"/>
-      <c r="N27" s="147"/>
-    </row>
-    <row r="28" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A28" s="154"/>
-      <c r="B28" s="155"/>
-      <c r="C28" s="162"/>
-      <c r="D28" s="163"/>
-      <c r="E28" s="164"/>
+      <c r="L27" s="130"/>
+      <c r="M27" s="130"/>
+      <c r="N27" s="130"/>
+    </row>
+    <row r="28" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A28" s="137"/>
+      <c r="B28" s="138"/>
+      <c r="C28" s="145"/>
+      <c r="D28" s="146"/>
+      <c r="E28" s="147"/>
       <c r="F28" s="26"/>
       <c r="G28" s="26"/>
       <c r="H28" s="26"/>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
       <c r="K28" s="123"/>
-      <c r="L28" s="147"/>
-      <c r="M28" s="147"/>
-      <c r="N28" s="147"/>
-    </row>
-    <row r="29" spans="1:14" s="2" customFormat="1" ht="30">
+      <c r="L28" s="130"/>
+      <c r="M28" s="130"/>
+      <c r="N28" s="130"/>
+    </row>
+    <row r="29" spans="1:14" s="2" customFormat="1" ht="31.5">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="16"/>
@@ -6558,7 +6558,7 @@
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="1:14" s="2" customFormat="1" ht="30">
+    <row r="30" spans="1:14" s="2" customFormat="1" ht="31.5">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -6578,8 +6578,8 @@
     <row r="32" spans="1:14" ht="16.5" customHeight="1"/>
     <row r="33" spans="17:22" ht="16.5" customHeight="1"/>
     <row r="34" spans="17:22" ht="16.5" customHeight="1"/>
-    <row r="37" spans="17:22" ht="24.9" customHeight="1"/>
-    <row r="38" spans="17:22" ht="24.9" customHeight="1">
+    <row r="37" spans="17:22" ht="24.95" customHeight="1"/>
+    <row r="38" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q38" s="18"/>
       <c r="R38" s="18"/>
       <c r="S38" s="18"/>
@@ -6587,28 +6587,28 @@
       <c r="U38" s="18"/>
       <c r="V38" s="18"/>
     </row>
-    <row r="39" spans="17:22" ht="24.9" customHeight="1">
+    <row r="39" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q39" s="19"/>
     </row>
-    <row r="40" spans="17:22" ht="24.9" customHeight="1">
+    <row r="40" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q40" s="19"/>
     </row>
-    <row r="41" spans="17:22" ht="24.9" customHeight="1">
+    <row r="41" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q41" s="19"/>
     </row>
-    <row r="42" spans="17:22" ht="24.9" customHeight="1">
+    <row r="42" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q42" s="19"/>
     </row>
-    <row r="43" spans="17:22" ht="24.9" customHeight="1">
+    <row r="43" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q43" s="19"/>
     </row>
-    <row r="44" spans="17:22" ht="24.9" customHeight="1">
+    <row r="44" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q44" s="19"/>
     </row>
-    <row r="45" spans="17:22" ht="24.9" customHeight="1">
+    <row r="45" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q45" s="19"/>
     </row>
-    <row r="46" spans="17:22" ht="24.9" customHeight="1">
+    <row r="46" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q46" s="19"/>
     </row>
     <row r="47" spans="17:22" ht="30" customHeight="1"/>
@@ -6629,12 +6629,19 @@
     <row r="62" ht="23.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A13:E19"/>
-    <mergeCell ref="F12:K12"/>
-    <mergeCell ref="F13:K19"/>
-    <mergeCell ref="L16:L19"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L2:M3"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="B4:H4"/>
     <mergeCell ref="K24:K28"/>
     <mergeCell ref="L24:N28"/>
     <mergeCell ref="A21:N21"/>
@@ -6642,19 +6649,12 @@
     <mergeCell ref="A24:B28"/>
     <mergeCell ref="C24:E28"/>
     <mergeCell ref="A23:N23"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="L2:M3"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E19"/>
+    <mergeCell ref="F12:K12"/>
+    <mergeCell ref="F13:K19"/>
+    <mergeCell ref="L16:L19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="L6">
@@ -6677,28 +6677,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:T30"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.09765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.8984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="7.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.19921875" customWidth="1"/>
-    <col min="9" max="9" width="4.8984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.09765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.8984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.19921875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.09765625" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.25" customWidth="1"/>
+    <col min="9" max="9" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="19.2">
+    <row r="1" spans="1:20" ht="17.25">
       <c r="A1" s="102" t="s">
         <v>303</v>
       </c>
@@ -6734,7 +6734,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="100" customFormat="1" ht="19.2">
+    <row r="2" spans="1:20" s="100" customFormat="1" ht="17.25">
       <c r="A2" s="97" t="s">
         <v>246</v>
       </c>
@@ -6786,7 +6786,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="3" spans="1:20" s="106" customFormat="1" ht="19.2">
+    <row r="3" spans="1:20" s="106" customFormat="1" ht="17.25">
       <c r="A3" s="106">
         <v>1</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:20" s="100" customFormat="1" ht="19.2">
+    <row r="4" spans="1:20" s="100" customFormat="1" ht="17.25">
       <c r="A4" s="100">
         <v>2</v>
       </c>
@@ -6976,7 +6976,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="19.2">
+    <row r="6" spans="1:20" ht="17.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -7044,7 +7044,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="7" spans="1:20" s="100" customFormat="1" ht="19.2">
+    <row r="7" spans="1:20" s="100" customFormat="1" ht="17.25">
       <c r="A7" s="100">
         <v>5</v>
       </c>
@@ -7112,7 +7112,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="19.2">
+    <row r="8" spans="1:20" ht="17.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -7985,14 +7985,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="12.59765625" style="55" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.625" style="55" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5" style="55" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.69921875" style="55"/>
+    <col min="3" max="16384" width="8.75" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="19.2">
+    <row r="1" spans="1:2" ht="17.25">
       <c r="A1" s="36" t="s">
         <v>198</v>
       </c>
@@ -8000,7 +8000,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="19.2">
+    <row r="2" spans="1:2" ht="17.25">
       <c r="A2" s="36" t="s">
         <v>200</v>
       </c>
@@ -8009,7 +8009,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="19.2">
+    <row r="3" spans="1:2" ht="17.25">
       <c r="A3" s="36" t="s">
         <v>201</v>
       </c>
@@ -8018,7 +8018,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="19.2">
+    <row r="4" spans="1:2" ht="17.25">
       <c r="A4" s="36" t="s">
         <v>202</v>
       </c>
@@ -8027,7 +8027,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="19.2">
+    <row r="5" spans="1:2" ht="17.25">
       <c r="A5" s="36" t="s">
         <v>203</v>
       </c>
@@ -8036,7 +8036,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="19.2">
+    <row r="6" spans="1:2" ht="17.25">
       <c r="A6" s="36" t="s">
         <v>241</v>
       </c>
@@ -8045,7 +8045,7 @@
         <v>5.3999999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="19.2">
+    <row r="7" spans="1:2" ht="17.25">
       <c r="A7" s="36" t="s">
         <v>242</v>
       </c>
@@ -8054,7 +8054,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="19.2">
+    <row r="8" spans="1:2" ht="17.25">
       <c r="A8" s="36" t="s">
         <v>245</v>
       </c>
@@ -8063,7 +8063,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="19.2">
+    <row r="9" spans="1:2" ht="17.25">
       <c r="A9" s="36" t="s">
         <v>311</v>
       </c>
